--- a/.claude/skills/invoice-tracker/output/cost_tracker.xlsx
+++ b/.claude/skills/invoice-tracker/output/cost_tracker.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Line Items'!$A$1:$O$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Anomalies'!$A$1:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Anomalies'!$A$1:$G$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8952,7 +8952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9184,30 +9184,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" s="3" t="n">
-        <v>13.85</v>
+        <v>16.38</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Charged 23/04/2025 (36 days before period start); period 29/05/2025-28/08/2025. "Attended site to re-fit fan control cabinet to the wall: 26/"</t>
+          <t>Maintenance: 20.40 this quarter vs prior average 4.02 (5.1x, higher).</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9220,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9234,15 +9230,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-1.03</v>
+        <v>13.85</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Charged 01/07/2025 (59 days before period start); period 29/08/2025-28/11/2025. "Attended site to program numbers as requested"</t>
+          <t>Charged 23/04/2025 (36 days before period start); period 29/05/2025-28/08/2025. "Attended site to re-fit fan control cabinet to the wall: 26/"</t>
         </is>
       </c>
     </row>
@@ -9269,15 +9265,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>3.4</v>
+        <v>-1.03</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Charged 15/07/2025 (45 days before period start); period 29/08/2025-28/11/2025. "Monitoring of CCTV"</t>
+          <t>Charged 01/07/2025 (59 days before period start); period 29/08/2025-28/11/2025. "Attended site to program numbers as requested"</t>
         </is>
       </c>
     </row>
@@ -9304,15 +9300,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ONESCO Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>11.03</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Charged 17/07/2025 (43 days before period start); period 29/08/2025-28/11/2025. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2025"</t>
+          <t>Charged 15/07/2025 (45 days before period start); period 29/08/2025-28/11/2025. "Monitoring of CCTV"</t>
         </is>
       </c>
     </row>
@@ -9329,25 +9325,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>ONESCO Ltd</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>86.5</v>
+        <v>11.03</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Charged 28/05/2026 (89 days after period end); period 29/11/2025-28/02/2026. "Management Fee: 01/03/2026 - 28/05/2026"</t>
+          <t>Charged 17/07/2025 (43 days before period start); period 29/08/2025-28/11/2025. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2025"</t>
         </is>
       </c>
     </row>
@@ -9364,25 +9360,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2.7</v>
+        <v>86.5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Charged 17/12/2025 (74 days before period start); period 01/03/2026-28/05/2026. "Quarterly fire alarm service"</t>
+          <t>Charged 28/05/2026 (89 days after period end); period 29/11/2025-28/02/2026. "Management Fee: 01/03/2026 - 28/05/2026"</t>
         </is>
       </c>
     </row>
@@ -9404,7 +9400,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -9413,11 +9409,11 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Charged 23/12/2025 (68 days before period start); period 01/03/2026-28/05/2026. "Door entry sim card change"</t>
+          <t>Charged 17/12/2025 (74 days before period start); period 01/03/2026-28/05/2026. "Quarterly fire alarm service"</t>
         </is>
       </c>
     </row>
@@ -9444,15 +9440,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>58.58</v>
+        <v>1.03</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Charged 28/01/2026 (32 days before period start); period 01/03/2026-28/05/2026. "Attended site to install new pump to replace missing pump"</t>
+          <t>Charged 23/12/2025 (68 days before period start); period 01/03/2026-28/05/2026. "Door entry sim card change"</t>
         </is>
       </c>
     </row>
@@ -9474,20 +9470,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>86.5</v>
+        <v>58.58</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Charged 28/08/2026 (92 days after period end); period 01/03/2026-28/05/2026. "Management Fee: 29/05/2026 - 28/08/2026"</t>
+          <t>Charged 28/01/2026 (32 days before period start); period 01/03/2026-28/05/2026. "Attended site to install new pump to replace missing pump"</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9495,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9507,15 +9503,22 @@
           <t>2013624</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASD Electrical Contractors Ltd</t>
-        </is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>86.5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>'ASD Electrical Contractors Ltd' billed in 3/3 prior quarters but is absent this quarter.</t>
+          <t>Charged 28/08/2026 (92 days after period end); period 01/03/2026-28/05/2026. "Management Fee: 29/05/2026 - 28/08/2026"</t>
         </is>
       </c>
     </row>
@@ -9527,26 +9530,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Dropped vendor</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Argyle Locksmiths</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>2.71</v>
+          <t>HDN- NIG - 2025-2026</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>'Argyle Locksmiths' appears this quarter but not in any prior quarter (cost 2.71).</t>
+          <t>'HDN- NIG - 2025-2026' billed in 2/2 prior quarters but is absent this quarter.</t>
         </is>
       </c>
     </row>
@@ -9558,30 +9558,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Stale service period</t>
+          <t>Dropped vendor</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1883739</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>13.85</v>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Service period 26/03/2025-23/04/2025 ends 36 days before the invoice quarter starts (29/05/2025). "Attended site to re-fit fan control cabinet to the"</t>
+          <t>'ASD Electrical Contractors Ltd' billed in 3/3 prior quarters but is absent this quarter.</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9586,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stale service period</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9601,959 +9594,824 @@
           <t>1933254</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ONESCO Ltd</t>
+          <t>AB Decorators</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>11.03</v>
+        <v>22.29</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Service period 26/06/2025-17/07/2025 ends 43 days before the invoice quarter starts (29/08/2025). "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2"</t>
+          <t>'AB Decorators' appears this quarter but not in any prior quarter (cost 22.29).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Abnormal category total</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Columbus Facilities Maintenance Ltd</t>
+        </is>
+      </c>
       <c r="F20" s="3" t="n">
-        <v>-120.6166666666667</v>
+        <v>18.85</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Electricity: 84.61 this quarter vs prior average 205.23 (0.4x, lower).</t>
+          <t>'Columbus Facilities Maintenance Ltd' appears this quarter but not in any prior quarter (cost 18.85).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Abnormal vendor total</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Hart Lifts Ltd</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>'Hart Lifts Ltd' appears this quarter but not in any prior quarter (cost 7.52).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Integra Building Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>'Integra Building Solutions Ltd' appears this quarter but not in any prior quarter (cost 2.23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>ONESCO Ltd</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>'ONESCO Ltd' appears this quarter but not in any prior quarter (cost 44.27).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PTSG Electrical Services Ltd</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>'PTSG Electrical Services Ltd' appears this quarter but not in any prior quarter (cost 22.94).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>APS Safety Systems Limited</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>'APS Safety Systems Limited' appears this quarter but not in any prior quarter (cost 10.51).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>City Drain Clear</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>'City Drain Clear' appears this quarter but not in any prior quarter (cost 3.34).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Cleansite Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>'Cleansite Solutions Ltd' appears this quarter but not in any prior quarter (cost 5.15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>DAWN ZURICH 26/27</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>'DAWN ZURICH 26/27' appears this quarter but not in any prior quarter (cost 11.43).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DAWN- INTACT-26-27</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>181.01</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>'DAWN- INTACT-26-27' appears this quarter but not in any prior quarter (cost 181.01).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>J.T. Mullen Building Services</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>'J.T. Mullen Building Services' appears this quarter but not in any prior quarter (cost 3.77).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>New vendor</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>'Argyle Locksmiths' appears this quarter but not in any prior quarter (cost 2.71).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>'attended site and downloaded cctv footage from mailbox camera' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>'attended site and removed snib from fire door dry riser door was detached from wall so attached timber batons to secure door' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>'attended site to re fit fan control cabinet to the wall' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>'emergency lighting repair' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>'quarterly service and inspection car park garage shutter' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>'replace faulty ball valves' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>'service checks of x booster set' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>'sim card charge for the gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>'sim card charges for gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>'vecon drive at pump' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>'water testing certification' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>'attended site to program numbers as requested' (e.g. Repairs) appeared in all 2 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>'quarterly fire alarm service' (e.g. Life System) appeared in all 2 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Stale service period</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>42.92666666666666</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd: 81.91 this quarter vs prior average 38.98 (2.1x, higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1883739</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Charged 30/04/2025 (29 days before period start); period 29/05/2025-28/08/2025. "Sim card charge for the GSM door access system: 01/04/2025 -"</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1883739</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Charged 23/05/2025 (6 days before period start); period 29/05/2025-28/08/2025. "Attended site and downloaded CCTV footage from mailbox camer"</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1883739</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>80.28</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Charged 29/08/2025 (1 days after period end); period 29/05/2025-28/08/2025. "Management Fee: 29/08/2025 - 28/11/2025"</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
+      <c r="F45" s="3" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Service period 26/03/2025-23/04/2025 ends 36 days before the invoice quarter starts (29/05/2025). "Attended site to re-fit fan control cabinet to the"</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Stale service period</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>1933254</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>PTSG Electrical Services Ltd</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Charged 08/08/2025 (21 days before period start); period 29/08/2025-28/11/2025. "Test &amp; Inspection of the Lighting Protection System"</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Charged 22/08/2025 (7 days before period start); period 29/08/2025-28/11/2025. "Door entry SIM card charge"</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Repairs</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AB Decorators</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>22.29</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Charged 26/08/2025 (3 days before period start); period 29/08/2025-28/11/2025. "Repairs to floor 11, 4, 1 &amp; stairwell to ground"</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>-7.42</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025. "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>80.28</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025. "Management Fee: 29/11/2025 - 28/02/2026"</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Grounds</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Cleansite Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Charged 17/11/2025 (12 days before period start); period 29/11/2025-28/02/2026. "Bulk uplift"</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Ritchie Mackenzie &amp; Co Ltd</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Charged 31/10/2025 (29 days before period start); period 29/11/2025-28/02/2026. "Service checks on 1 x Two Pump Booster Set"</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Hart Lifts Ltd</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Charged 14/11/2025 (15 days before period start); period 29/11/2025-28/02/2026. "Repairs to lift controller unit"</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Hart Lifts Ltd</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Charged 21/11/2025 (8 days before period start); period 29/11/2025-28/02/2026. "Renewed damaged lift door spring"</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Integra Building Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Charged 25/11/2025 (4 days before period start); period 29/11/2025-28/02/2026. "Replace dry riser inlet lock"</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>-7.72</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Charged 01/03/2026 (1 days after period end); period 29/11/2025-28/02/2026. "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Charged 31/01/2026 (29 days before period start); period 01/03/2026-28/05/2026. "Door entry SIM card charge"</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Charged 15/02/2026 (14 days before period start); period 01/03/2026-28/05/2026. "Reset fire alarm system"</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Hart Lifts Ltd</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Charged 30/01/2026 (30 days before period start); period 01/03/2026-28/05/2026. "Repairs to lift (mis-use)"</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Argyle Locksmiths</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Charged 05/02/2026 (24 days before period start); period 01/03/2026-28/05/2026. "Lower car park door reset code"</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Charged 16/02/2026 (13 days before period start); period 01/03/2026-28/05/2026. "Repair to upper car park shutter"</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>-7.72</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Charged 29/05/2026 (1 days after period end); period 01/03/2026-28/05/2026. "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Credit / negative line</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1883739</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>-7.42</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-7.42 — "E-billing Discount: 29/08/2025 - 28/11/2025"</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Credit / negative line</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-1.03 — "Attended site to program numbers as requested"</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Credit / negative line</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>-7.42</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-7.42 — "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Credit / negative line</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>-7.72</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-7.72 — "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Credit / negative line</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>ONESCO Ltd</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>-7.72</v>
+        <v>11.03</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-7.72 — "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+          <t>Service period 26/06/2025-17/07/2025 ends 43 days before the invoice quarter starts (29/08/2025). "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2"</t>
         </is>
       </c>
     </row>
@@ -10565,23 +10423,26 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>HDN- NIG - 2025-2026</t>
-        </is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" s="3" t="n">
+        <v>-228.33</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>'HDN- NIG - 2025-2026' billed in 2/3 prior quarters but is absent this quarter.</t>
+          <t>Electricity: 144.38 this quarter vs prior average 372.71 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10593,23 +10454,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>VWS (UK) T/A Veolia Water Technologies</t>
-        </is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" s="3" t="n">
+        <v>-159.955</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>'VWS (UK) T/A Veolia Water Technologies' billed in 2/3 prior quarters but is absent this quarter.</t>
+          <t>Electricity: 98.59 this quarter vs prior average 258.54 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10621,35 +10485,1121 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>Abnormal category total</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" s="3" t="n">
+        <v>-35.585</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Life System: 30.35 this quarter vs prior average 65.94 (0.5x, lower).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Abnormal category total</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" s="3" t="n">
+        <v>-77.255</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Repairs: 45.04 this quarter vs prior average 122.30 (0.4x, lower).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Abnormal category total</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" s="3" t="n">
+        <v>-120.6166666666667</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Electricity: 84.61 this quarter vs prior average 205.23 (0.4x, lower).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Abnormal vendor total</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-32.32</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd: 2.26 this quarter vs prior average 34.58 (0.1x, lower).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Abnormal vendor total</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>42.92666666666666</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd: 81.91 this quarter vs prior average 38.98 (2.1x, higher).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Charged 30/04/2025 (29 days before period start); period 29/05/2025-28/08/2025. "Sim card charge for the GSM door access system: 01/04/2025 -"</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Charged 23/05/2025 (6 days before period start); period 29/05/2025-28/08/2025. "Attended site and downloaded CCTV footage from mailbox camer"</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>80.28</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Charged 29/08/2025 (1 days after period end); period 29/05/2025-28/08/2025. "Management Fee: 29/08/2025 - 28/11/2025"</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PTSG Electrical Services Ltd</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Charged 08/08/2025 (21 days before period start); period 29/08/2025-28/11/2025. "Test &amp; Inspection of the Lighting Protection System"</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Charged 22/08/2025 (7 days before period start); period 29/08/2025-28/11/2025. "Door entry SIM card charge"</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AB Decorators</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Charged 26/08/2025 (3 days before period start); period 29/08/2025-28/11/2025. "Repairs to floor 11, 4, 1 &amp; stairwell to ground"</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025. "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>80.28</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025. "Management Fee: 29/11/2025 - 28/02/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Grounds</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Cleansite Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Charged 17/11/2025 (12 days before period start); period 29/11/2025-28/02/2026. "Bulk uplift"</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Charged 31/10/2025 (29 days before period start); period 29/11/2025-28/02/2026. "Service checks on 1 x Two Pump Booster Set"</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Hart Lifts Ltd</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Charged 14/11/2025 (15 days before period start); period 29/11/2025-28/02/2026. "Repairs to lift controller unit"</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Hart Lifts Ltd</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Charged 21/11/2025 (8 days before period start); period 29/11/2025-28/02/2026. "Renewed damaged lift door spring"</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Integra Building Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Charged 25/11/2025 (4 days before period start); period 29/11/2025-28/02/2026. "Replace dry riser inlet lock"</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Charged 01/03/2026 (1 days after period end); period 29/11/2025-28/02/2026. "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Charged 31/01/2026 (29 days before period start); period 01/03/2026-28/05/2026. "Door entry SIM card charge"</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Charged 15/02/2026 (14 days before period start); period 01/03/2026-28/05/2026. "Reset fire alarm system"</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Hart Lifts Ltd</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Charged 30/01/2026 (30 days before period start); period 01/03/2026-28/05/2026. "Repairs to lift (mis-use)"</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Charged 05/02/2026 (24 days before period start); period 01/03/2026-28/05/2026. "Lower car park door reset code"</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Charged 16/02/2026 (13 days before period start); period 01/03/2026-28/05/2026. "Repair to upper car park shutter"</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Charged 29/05/2026 (1 days after period end); period 01/03/2026-28/05/2026. "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-7.42 — "E-billing Discount: 29/08/2025 - 28/11/2025"</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-1.03 — "Attended site to program numbers as requested"</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-7.42 — "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-7.72 — "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-7.72 — "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>HDN- NIG - 2025-2026</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>'HDN- NIG - 2025-2026' billed in 2/3 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>VWS (UK) T/A Veolia Water Technologies</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>'VWS (UK) T/A Veolia Water Technologies' billed in 2/3 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>Stale service period</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>1883739</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Life System</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F81" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Service period 01/04/2025-30/04/2025 ends 29 days before the invoice quarter starts (29/05/2025). "Sim card charge for the GSM door access system: 01"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G49"/>
+  <autoFilter ref="A1:G81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/.claude/skills/invoice-tracker/output/cost_tracker.xlsx
+++ b/.claude/skills/invoice-tracker/output/cost_tracker.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Line Items'!$A$1:$O$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Anomalies'!$A$1:$G$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Anomalies'!$A$1:$G$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2487,73 +2487,77 @@
       <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>1933254</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>14/11/2025</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>29/08/2025</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>28/11/2025</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>01/09/2025</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Ecotricity DD</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Common electricity supply 1: 01/04/2025 - 01/10/2025</t>
         </is>
       </c>
-      <c r="J26" s="3" t="n">
+      <c r="J26" s="9" t="n">
         <v>5053.31</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>1/35</t>
         </is>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="9" t="n">
         <v>144.38</v>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>01/04/2025</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N26" s="8" t="inlineStr">
         <is>
           <t>01/10/2025</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" s="8" t="inlineStr">
+        <is>
+          <t>Cross-invoice duplicate charge</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2946,142 +2950,150 @@
       <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>1933254</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>14/11/2025</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>29/08/2025</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr">
         <is>
           <t>28/11/2025</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
         <is>
           <t>Life System</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="8" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Quarterly service and inspection of car park garage ventilation: 01/06/2025 - 30/09/2025</t>
         </is>
       </c>
-      <c r="J33" s="3" t="n">
+      <c r="J33" s="9" t="n">
         <v>94.2</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t>1/18</t>
         </is>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>5.23</v>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>01/06/2025</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="8" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" s="8" t="inlineStr">
+        <is>
+          <t>Cross-invoice duplicate charge</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>1933254</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>14/11/2025</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>29/08/2025</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr">
         <is>
           <t>28/11/2025</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>Life System</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>Quarterly smoke extract sys service: 01/06/2025 - 30/09/2025</t>
         </is>
       </c>
-      <c r="J34" s="3" t="n">
+      <c r="J34" s="9" t="n">
         <v>160.2</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="8" t="inlineStr">
         <is>
           <t>1/35</t>
         </is>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>4.57</v>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t>01/06/2025</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="8" t="inlineStr">
         <is>
           <t>30/09/2025</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" s="8" t="inlineStr">
+        <is>
+          <t>Cross-invoice duplicate charge</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4441,73 +4453,77 @@
       <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>1968807</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>23/02/2026</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>29/11/2025</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>28/02/2026</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>01/12/2025</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>Ecotricity DD</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>Common electricity supply 1: 01/06/2025 - 01/01/2026</t>
         </is>
       </c>
-      <c r="J56" s="3" t="n">
+      <c r="J56" s="9" t="n">
         <v>3450.99</v>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>1/35</t>
         </is>
       </c>
-      <c r="L56" s="3" t="n">
+      <c r="L56" s="9" t="n">
         <v>98.59</v>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>01/06/2025</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="N56" s="8" t="inlineStr">
         <is>
           <t>01/01/2026</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>Cross-invoice duplicate charge</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6691,142 +6707,150 @@
       <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="8" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>2013624</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>Life System</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>Quarterly car park shutter inspection: 24/12/2025 - 31/03/2026</t>
         </is>
       </c>
-      <c r="J90" s="3" t="n">
+      <c r="J90" s="9" t="n">
         <v>260.04</v>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K90" s="8" t="inlineStr">
         <is>
           <t>1/18</t>
         </is>
       </c>
-      <c r="L90" s="3" t="n">
+      <c r="L90" s="9" t="n">
         <v>14.45</v>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="M90" s="8" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr">
+      <c r="N90" s="8" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>Possible duplicate line (same invoice)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>2025/26</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>2013624</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>01/03/2026</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>Life System</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
         <is>
           <t>Quarterly car park shutter inspection x2: 24/12/2025 - 31/03/2026</t>
         </is>
       </c>
-      <c r="J91" s="3" t="n">
+      <c r="J91" s="9" t="n">
         <v>260.04</v>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K91" s="8" t="inlineStr">
         <is>
           <t>1/18</t>
         </is>
       </c>
-      <c r="L91" s="3" t="n">
+      <c r="L91" s="9" t="n">
         <v>14.45</v>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="M91" s="8" t="inlineStr">
         <is>
           <t>24/12/2025</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr">
+      <c r="N91" s="8" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
+      <c r="O91" s="8" t="inlineStr">
+        <is>
+          <t>Possible duplicate line (same invoice)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8952,7 +8976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9032,7 +9056,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Charged 31/01/2024 (484 days before period start); period 29/05/2025-28/08/2025. "Common electricity supply : 12/10/2023 - 31/01/2024"</t>
+          <t>Charged 31/01/2024 (484 days before period start); period 29/05/2025-28/08/2025; £326.98. "Common electricity supply : 12/10/2023 - 31/01/2024"</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9091,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Charged 31/08/2024 (271 days before period start); period 29/05/2025-28/08/2025. "vecon drive at pump"</t>
+          <t>Charged 31/08/2024 (271 days before period start); period 29/05/2025-28/08/2025; £56.27. "vecon drive at pump"</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9126,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Charged 31/10/2024 (210 days before period start); period 29/05/2025-28/08/2025. "Service checks of 1 x booster set"</t>
+          <t>Charged 31/10/2024 (210 days before period start); period 29/05/2025-28/08/2025; £6.17. "Service checks of 1 x booster set"</t>
         </is>
       </c>
     </row>
@@ -9149,61 +9173,65 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Possible duplicate line (same invoice)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2x same vendor/period/cost with different descriptions: PTM Security Solutions Ltd 24/12/2025-31/03/2026 14.45 each — "Quarterly car park shutter inspection: 2" | "Quarterly car park shutter inspection x2"</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Stale service period</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>1883739</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>SSE Scottish Hydro - A/C 00000000</t>
         </is>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>326.98</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Service period 12/10/2023-31/01/2024 ends 484 days before the invoice quarter starts (29/05/2025). "Common electricity supply : 12/10/2023 - 31/01/202"</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" s="3" t="n">
-        <v>16.38</v>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Maintenance: 20.40 this quarter vs prior average 4.02 (5.1x, higher).</t>
+          <t>Service period 12/10/2023-31/01/2024 ends 484 days before the invoice quarter starts (29/05/2025); £326.98. "Common electricity supply : 12/10/2023 - 31/01/202"</t>
         </is>
       </c>
     </row>
@@ -9215,30 +9243,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" s="3" t="n">
-        <v>13.85</v>
+        <v>16.38</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Charged 23/04/2025 (36 days before period start); period 29/05/2025-28/08/2025. "Attended site to re-fit fan control cabinet to the wall: 26/"</t>
+          <t>Maintenance: 20.40 this quarter vs prior average 4.02 (5.1x, higher).</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9279,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9265,15 +9289,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>-1.03</v>
+        <v>13.85</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Charged 01/07/2025 (59 days before period start); period 29/08/2025-28/11/2025. "Attended site to program numbers as requested"</t>
+          <t>Charged 23/04/2025 (36 days before period start); period 29/05/2025-28/08/2025; £13.85. "Attended site to re-fit fan control cabinet to the wall: 26/"</t>
         </is>
       </c>
     </row>
@@ -9300,15 +9324,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>3.4</v>
+        <v>-1.03</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Charged 15/07/2025 (45 days before period start); period 29/08/2025-28/11/2025. "Monitoring of CCTV"</t>
+          <t>Charged 01/07/2025 (59 days before period start); period 29/08/2025-28/11/2025; £-1.03. "Attended site to program numbers as requested"</t>
         </is>
       </c>
     </row>
@@ -9335,15 +9359,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ONESCO Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>11.03</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Charged 17/07/2025 (43 days before period start); period 29/08/2025-28/11/2025. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2025"</t>
+          <t>Charged 15/07/2025 (45 days before period start); period 29/08/2025-28/11/2025; £3.40. "Monitoring of CCTV"</t>
         </is>
       </c>
     </row>
@@ -9360,25 +9384,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>ONESCO Ltd</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>86.5</v>
+        <v>11.03</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Charged 28/05/2026 (89 days after period end); period 29/11/2025-28/02/2026. "Management Fee: 01/03/2026 - 28/05/2026"</t>
+          <t>Charged 17/07/2025 (43 days before period start); period 29/08/2025-28/11/2025; £11.03. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2025"</t>
         </is>
       </c>
     </row>
@@ -9395,25 +9419,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2.7</v>
+        <v>86.5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Charged 17/12/2025 (74 days before period start); period 01/03/2026-28/05/2026. "Quarterly fire alarm service"</t>
+          <t>Charged 28/05/2026 (89 days after period end); period 29/11/2025-28/02/2026; £86.50. "Management Fee: 01/03/2026 - 28/05/2026"</t>
         </is>
       </c>
     </row>
@@ -9435,7 +9459,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -9444,11 +9468,11 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.03</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Charged 23/12/2025 (68 days before period start); period 01/03/2026-28/05/2026. "Door entry sim card change"</t>
+          <t>Charged 17/12/2025 (74 days before period start); period 01/03/2026-28/05/2026; £2.70. "Quarterly fire alarm service"</t>
         </is>
       </c>
     </row>
@@ -9475,15 +9499,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>58.58</v>
+        <v>1.03</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Charged 28/01/2026 (32 days before period start); period 01/03/2026-28/05/2026. "Attended site to install new pump to replace missing pump"</t>
+          <t>Charged 23/12/2025 (68 days before period start); period 01/03/2026-28/05/2026; £1.03. "Door entry sim card change"</t>
         </is>
       </c>
     </row>
@@ -9505,20 +9529,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>86.5</v>
+        <v>58.58</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Charged 28/08/2026 (92 days after period end); period 01/03/2026-28/05/2026. "Management Fee: 29/05/2026 - 28/08/2026"</t>
+          <t>Charged 28/01/2026 (32 days before period start); period 01/03/2026-28/05/2026; £58.58. "Attended site to install new pump to replace missing pump"</t>
         </is>
       </c>
     </row>
@@ -9530,23 +9554,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HDN- NIG - 2025-2026</t>
-        </is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>86.5</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>'HDN- NIG - 2025-2026' billed in 2/2 prior quarters but is absent this quarter.</t>
+          <t>Charged 28/08/2026 (92 days after period end); period 01/03/2026-28/05/2026; £86.50. "Management Fee: 29/05/2026 - 28/08/2026"</t>
         </is>
       </c>
     </row>
@@ -9558,23 +9589,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASD Electrical Contractors Ltd</t>
-        </is>
+          <t>Ecotricity DD</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>144.38</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>'ASD Electrical Contractors Ltd' billed in 3/3 prior quarters but is absent this quarter.</t>
+          <t>Ecotricity DD: service 01/04/2025-01/10/2025 overlaps 92d with inv 1883739 15/03/2025-01/07/2025; £144.38. "Common electricity supply 1: 01/04/2025 " vs "Common electricity supply 1: 15/03/2025 "</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9624,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9594,18 +9632,22 @@
           <t>1933254</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AB Decorators</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>22.29</v>
+        <v>5.23</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>'AB Decorators' appears this quarter but not in any prior quarter (cost 22.29).</t>
+          <t>PTM Security Solutions Ltd: service 01/06/2025-30/09/2025 overlaps 36d with inv 1883739 26/06/2025-31/07/2025; £5.23. "Quarterly service and inspection of car " vs "Door entry SIM card charge: 26/06/2025 -"</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9659,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9625,18 +9667,22 @@
           <t>1933254</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Columbus Facilities Maintenance Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>18.85</v>
+        <v>5.23</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>'Columbus Facilities Maintenance Ltd' appears this quarter but not in any prior quarter (cost 18.85).</t>
+          <t>PTM Security Solutions Ltd: service 01/06/2025-30/09/2025 overlaps 122d with inv 1883739 01/06/2025-30/09/2025; £5.23. "Quarterly service and inspection of car " vs "Quarterly service and inspection car par"</t>
         </is>
       </c>
     </row>
@@ -9648,26 +9694,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hart Lifts Ltd</t>
+          <t>Ecotricity DD</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>7.52</v>
+        <v>98.59</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>'Hart Lifts Ltd' appears this quarter but not in any prior quarter (cost 7.52).</t>
+          <t>Ecotricity DD: service 01/06/2025-01/01/2026 overlaps 123d with inv 1933254 01/04/2025-01/10/2025; £98.59. "Common electricity supply 1: 01/06/2025 " vs "Common electricity supply 1: 01/04/2025 "</t>
         </is>
       </c>
     </row>
@@ -9679,26 +9729,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Dropped vendor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Integra Building Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>2.23</v>
+          <t>HDN- NIG - 2025-2026</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>'Integra Building Solutions Ltd' appears this quarter but not in any prior quarter (cost 2.23).</t>
+          <t>'HDN- NIG - 2025-2026' billed in 2/2 prior quarters but is absent this quarter.</t>
         </is>
       </c>
     </row>
@@ -9710,26 +9757,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Dropped vendor</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ONESCO Ltd</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>44.27</v>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>'ONESCO Ltd' appears this quarter but not in any prior quarter (cost 44.27).</t>
+          <t>'ASD Electrical Contractors Ltd' billed in 3/3 prior quarters but is absent this quarter.</t>
         </is>
       </c>
     </row>
@@ -9752,15 +9796,15 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PTSG Electrical Services Ltd</t>
+          <t>AB Decorators</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>22.94</v>
+        <v>22.29</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>'PTSG Electrical Services Ltd' appears this quarter but not in any prior quarter (cost 22.94).</t>
+          <t>'AB Decorators' appears this quarter but not in any prior quarter (cost 22.29).</t>
         </is>
       </c>
     </row>
@@ -9777,21 +9821,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>APS Safety Systems Limited</t>
+          <t>Columbus Facilities Maintenance Ltd</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>10.51</v>
+        <v>18.85</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>'APS Safety Systems Limited' appears this quarter but not in any prior quarter (cost 10.51).</t>
+          <t>'Columbus Facilities Maintenance Ltd' appears this quarter but not in any prior quarter (cost 18.85).</t>
         </is>
       </c>
     </row>
@@ -9808,21 +9852,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>City Drain Clear</t>
+          <t>Hart Lifts Ltd</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>3.34</v>
+        <v>7.52</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>'City Drain Clear' appears this quarter but not in any prior quarter (cost 3.34).</t>
+          <t>'Hart Lifts Ltd' appears this quarter but not in any prior quarter (cost 7.52).</t>
         </is>
       </c>
     </row>
@@ -9839,21 +9883,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cleansite Solutions Ltd</t>
+          <t>Integra Building Solutions Ltd</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.15</v>
+        <v>2.23</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>'Cleansite Solutions Ltd' appears this quarter but not in any prior quarter (cost 5.15).</t>
+          <t>'Integra Building Solutions Ltd' appears this quarter but not in any prior quarter (cost 2.23).</t>
         </is>
       </c>
     </row>
@@ -9870,21 +9914,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DAWN ZURICH 26/27</t>
+          <t>ONESCO Ltd</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>11.43</v>
+        <v>44.27</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>'DAWN ZURICH 26/27' appears this quarter but not in any prior quarter (cost 11.43).</t>
+          <t>'ONESCO Ltd' appears this quarter but not in any prior quarter (cost 44.27).</t>
         </is>
       </c>
     </row>
@@ -9901,21 +9945,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DAWN- INTACT-26-27</t>
+          <t>PTSG Electrical Services Ltd</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>181.01</v>
+        <v>22.94</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>'DAWN- INTACT-26-27' appears this quarter but not in any prior quarter (cost 181.01).</t>
+          <t>'PTSG Electrical Services Ltd' appears this quarter but not in any prior quarter (cost 22.94).</t>
         </is>
       </c>
     </row>
@@ -9938,15 +9982,15 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>J.T. Mullen Building Services</t>
+          <t>APS Safety Systems Limited</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>3.77</v>
+        <v>10.51</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>'J.T. Mullen Building Services' appears this quarter but not in any prior quarter (cost 3.77).</t>
+          <t>'APS Safety Systems Limited' appears this quarter but not in any prior quarter (cost 10.51).</t>
         </is>
       </c>
     </row>
@@ -9963,21 +10007,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Argyle Locksmiths</t>
+          <t>City Drain Clear</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>2.71</v>
+        <v>3.34</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>'Argyle Locksmiths' appears this quarter but not in any prior quarter (cost 2.71).</t>
+          <t>'City Drain Clear' appears this quarter but not in any prior quarter (cost 3.34).</t>
         </is>
       </c>
     </row>
@@ -9989,23 +10033,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cleansite Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>5.15</v>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>'attended site and downloaded cctv footage from mailbox camera' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'Cleansite Solutions Ltd' appears this quarter but not in any prior quarter (cost 5.15).</t>
         </is>
       </c>
     </row>
@@ -10017,23 +10064,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DAWN ZURICH 26/27</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>11.43</v>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>'attended site and removed snib from fire door dry riser door was detached from wall so attached timber batons to secure door' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'DAWN ZURICH 26/27' appears this quarter but not in any prior quarter (cost 11.43).</t>
         </is>
       </c>
     </row>
@@ -10045,23 +10095,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DAWN- INTACT-26-27</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>181.01</v>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>'attended site to re fit fan control cabinet to the wall' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'DAWN- INTACT-26-27' appears this quarter but not in any prior quarter (cost 181.01).</t>
         </is>
       </c>
     </row>
@@ -10073,23 +10126,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>J.T. Mullen Building Services</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>3.77</v>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>'emergency lighting repair' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'J.T. Mullen Building Services' appears this quarter but not in any prior quarter (cost 3.77).</t>
         </is>
       </c>
     </row>
@@ -10101,23 +10157,26 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2.71</v>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>'quarterly service and inspection car park garage shutter' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'Argyle Locksmiths' appears this quarter but not in any prior quarter (cost 2.71).</t>
         </is>
       </c>
     </row>
@@ -10139,13 +10198,13 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>'replace faulty ball valves' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'attended site and downloaded cctv footage from mailbox camera' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10232,7 @@
       <c r="E38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>'service checks of x booster set' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'attended site and removed snib from fire door dry riser door was detached from wall so attached timber batons to secure door' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10195,13 +10254,13 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>'sim card charge for the gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'attended site to re fit fan control cabinet to the wall' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10288,7 @@
       <c r="E40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>'sim card charges for gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'emergency lighting repair' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10316,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>'vecon drive at pump' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'quarterly service and inspection car park garage shutter' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10279,13 +10338,13 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>'water testing certification' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'replace faulty ball valves' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10361,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -10313,7 +10372,7 @@
       <c r="E43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>'attended site to program numbers as requested' (e.g. Repairs) appeared in all 2 prior quarters but not this quarter.</t>
+          <t>'service checks of x booster set' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10389,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -10341,7 +10400,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>'quarterly fire alarm service' (e.g. Life System) appeared in all 2 prior quarters but not this quarter.</t>
+          <t>'sim card charge for the gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10353,30 +10412,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Stale service period</t>
+          <t>Recurring item missing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>13.85</v>
-      </c>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Service period 26/03/2025-23/04/2025 ends 36 days before the invoice quarter starts (29/05/2025). "Attended site to re-fit fan control cabinet to the"</t>
+          <t>'sim card charges for gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10388,185 +10440,177 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>'vecon drive at pump' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>'water testing certification' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>'attended site to program numbers as requested' (e.g. Repairs) appeared in all 2 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>'quarterly fire alarm service' (e.g. Life System) appeared in all 2 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Stale service period</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Service period 26/03/2025-23/04/2025 ends 36 days before the invoice quarter starts (29/05/2025); £13.85. "Attended site to re-fit fan control cabinet to the"</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Stale service period</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
         <is>
           <t>1933254</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Repairs</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>ONESCO Ltd</t>
         </is>
       </c>
-      <c r="F46" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>11.03</v>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Service period 26/06/2025-17/07/2025 ends 43 days before the invoice quarter starts (29/08/2025). "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2"</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" s="3" t="n">
-        <v>-228.33</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Electricity: 144.38 this quarter vs prior average 372.71 (0.4x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" s="3" t="n">
-        <v>-159.955</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Electricity: 98.59 this quarter vs prior average 258.54 (0.4x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" s="3" t="n">
-        <v>-35.585</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Life System: 30.35 this quarter vs prior average 65.94 (0.5x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" s="3" t="n">
-        <v>-77.255</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Repairs: 45.04 this quarter vs prior average 122.30 (0.4x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" s="3" t="n">
-        <v>-120.6166666666667</v>
-      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Electricity: 84.61 this quarter vs prior average 205.23 (0.4x, lower).</t>
+          <t>Service period 26/06/2025-17/07/2025 ends 43 days before the invoice quarter starts (29/08/2025); £11.03. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2"</t>
         </is>
       </c>
     </row>
@@ -10578,26 +10622,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Abnormal vendor total</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ASD Electrical Contractors Ltd</t>
-        </is>
-      </c>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" s="3" t="n">
-        <v>-32.32</v>
+        <v>-228.33</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ASD Electrical Contractors Ltd: 2.26 this quarter vs prior average 34.58 (0.1x, lower).</t>
+          <t>Electricity: 144.38 this quarter vs prior average 372.71 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10609,26 +10653,26 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Abnormal vendor total</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" s="3" t="n">
-        <v>42.92666666666666</v>
+        <v>-159.955</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd: 81.91 this quarter vs prior average 38.98 (2.1x, higher).</t>
+          <t>Electricity: 98.59 this quarter vs prior average 258.54 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10640,12 +10684,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -10653,17 +10697,13 @@
           <t>Life System</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" s="3" t="n">
-        <v>0.29</v>
+        <v>-35.585</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Charged 30/04/2025 (29 days before period start); period 29/05/2025-28/08/2025. "Sim card charge for the GSM door access system: 01/04/2025 -"</t>
+          <t>Life System: 30.35 this quarter vs prior average 65.94 (0.5x, lower).</t>
         </is>
       </c>
     </row>
@@ -10675,30 +10715,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" s="3" t="n">
-        <v>4.25</v>
+        <v>-77.255</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Charged 23/05/2025 (6 days before period start); period 29/05/2025-28/08/2025. "Attended site and downloaded CCTV footage from mailbox camer"</t>
+          <t>Repairs: 45.04 this quarter vs prior average 122.30 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10710,30 +10746,26 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" s="3" t="n">
-        <v>80.28</v>
+        <v>-120.6166666666667</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Charged 29/08/2025 (1 days after period end); period 29/05/2025-28/08/2025. "Management Fee: 29/08/2025 - 28/11/2025"</t>
+          <t>Electricity: 84.61 this quarter vs prior average 205.23 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10745,30 +10777,26 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal vendor total</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PTSG Electrical Services Ltd</t>
+          <t>ASD Electrical Contractors Ltd</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>7.2</v>
+        <v>-32.32</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Charged 08/08/2025 (21 days before period start); period 29/08/2025-28/11/2025. "Test &amp; Inspection of the Lighting Protection System"</t>
+          <t>ASD Electrical Contractors Ltd: 2.26 this quarter vs prior average 34.58 (0.1x, lower).</t>
         </is>
       </c>
     </row>
@@ -10780,30 +10808,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal vendor total</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3</v>
+        <v>42.92666666666666</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Charged 22/08/2025 (7 days before period start); period 29/08/2025-28/11/2025. "Door entry SIM card charge"</t>
+          <t>PTM Security Solutions Ltd: 81.91 this quarter vs prior average 38.98 (2.1x, higher).</t>
         </is>
       </c>
     </row>
@@ -10820,25 +10844,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AB Decorators</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>22.29</v>
+        <v>0.29</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Charged 26/08/2025 (3 days before period start); period 29/08/2025-28/11/2025. "Repairs to floor 11, 4, 1 &amp; stairwell to ground"</t>
+          <t>Charged 30/04/2025 (29 days before period start); period 29/05/2025-28/08/2025; £0.29. "Sim card charge for the GSM door access system: 01/04/2025 -"</t>
         </is>
       </c>
     </row>
@@ -10855,25 +10879,25 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>-7.42</v>
+        <v>4.25</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025. "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+          <t>Charged 23/05/2025 (6 days before period start); period 29/05/2025-28/08/2025; £4.25. "Attended site and downloaded CCTV footage from mailbox camer"</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10914,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10908,7 +10932,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025. "Management Fee: 29/11/2025 - 28/02/2026"</t>
+          <t>Charged 29/08/2025 (1 days after period end); period 29/05/2025-28/08/2025; £80.28. "Management Fee: 29/08/2025 - 28/11/2025"</t>
         </is>
       </c>
     </row>
@@ -10925,25 +10949,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Grounds</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cleansite Solutions Ltd</t>
+          <t>PTSG Electrical Services Ltd</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>5.15</v>
+        <v>7.2</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Charged 17/11/2025 (12 days before period start); period 29/11/2025-28/02/2026. "Bulk uplift"</t>
+          <t>Charged 08/08/2025 (21 days before period start); period 29/08/2025-28/11/2025; £7.20. "Test &amp; Inspection of the Lighting Protection System"</t>
         </is>
       </c>
     </row>
@@ -10960,25 +10984,25 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>5.83</v>
+        <v>0.3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Charged 31/10/2025 (29 days before period start); period 29/11/2025-28/02/2026. "Service checks on 1 x Two Pump Booster Set"</t>
+          <t>Charged 22/08/2025 (7 days before period start); period 29/08/2025-28/11/2025; £0.30. "Door entry SIM card charge"</t>
         </is>
       </c>
     </row>
@@ -10995,7 +11019,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -11005,15 +11029,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hart Lifts Ltd</t>
+          <t>AB Decorators</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>8.33</v>
+        <v>22.29</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Charged 14/11/2025 (15 days before period start); period 29/11/2025-28/02/2026. "Repairs to lift controller unit"</t>
+          <t>Charged 26/08/2025 (3 days before period start); period 29/08/2025-28/11/2025; £22.29. "Repairs to floor 11, 4, 1 &amp; stairwell to ground"</t>
         </is>
       </c>
     </row>
@@ -11030,25 +11054,25 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hart Lifts Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>5.48</v>
+        <v>-7.42</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Charged 21/11/2025 (8 days before period start); period 29/11/2025-28/02/2026. "Renewed damaged lift door spring"</t>
+          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025; £-7.42. "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
         </is>
       </c>
     </row>
@@ -11065,25 +11089,25 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Integra Building Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>2.57</v>
+        <v>80.28</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Charged 25/11/2025 (4 days before period start); period 29/11/2025-28/02/2026. "Replace dry riser inlet lock"</t>
+          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025; £80.28. "Management Fee: 29/11/2025 - 28/02/2026"</t>
         </is>
       </c>
     </row>
@@ -11105,20 +11129,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Cleansite Solutions Ltd</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>-7.72</v>
+        <v>5.15</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Charged 01/03/2026 (1 days after period end); period 29/11/2025-28/02/2026. "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+          <t>Charged 17/11/2025 (12 days before period start); period 29/11/2025-28/02/2026; £5.15. "Bulk uplift"</t>
         </is>
       </c>
     </row>
@@ -11135,25 +11159,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.31</v>
+        <v>5.83</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Charged 31/01/2026 (29 days before period start); period 01/03/2026-28/05/2026. "Door entry SIM card charge"</t>
+          <t>Charged 31/10/2025 (29 days before period start); period 29/11/2025-28/02/2026; £5.83. "Service checks on 1 x Two Pump Booster Set"</t>
         </is>
       </c>
     </row>
@@ -11170,25 +11194,25 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Hart Lifts Ltd</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>5.53</v>
+        <v>8.33</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Charged 15/02/2026 (14 days before period start); period 01/03/2026-28/05/2026. "Reset fire alarm system"</t>
+          <t>Charged 14/11/2025 (15 days before period start); period 29/11/2025-28/02/2026; £8.33. "Repairs to lift controller unit"</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11229,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11219,11 +11243,11 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>4.6</v>
+        <v>5.48</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Charged 30/01/2026 (30 days before period start); period 01/03/2026-28/05/2026. "Repairs to lift (mis-use)"</t>
+          <t>Charged 21/11/2025 (8 days before period start); period 29/11/2025-28/02/2026; £5.48. "Renewed damaged lift door spring"</t>
         </is>
       </c>
     </row>
@@ -11240,7 +11264,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11250,15 +11274,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Argyle Locksmiths</t>
+          <t>Integra Building Solutions Ltd</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Charged 05/02/2026 (24 days before period start); period 01/03/2026-28/05/2026. "Lower car park door reset code"</t>
+          <t>Charged 25/11/2025 (4 days before period start); period 29/11/2025-28/02/2026; £2.57. "Replace dry riser inlet lock"</t>
         </is>
       </c>
     </row>
@@ -11275,25 +11299,25 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>13.2</v>
+        <v>-7.72</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Charged 16/02/2026 (13 days before period start); period 01/03/2026-28/05/2026. "Repair to upper car park shutter"</t>
+          <t>Charged 01/03/2026 (1 days after period end); period 29/11/2025-28/02/2026; £-7.72. "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
         </is>
       </c>
     </row>
@@ -11315,20 +11339,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>-7.72</v>
+        <v>0.31</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Charged 29/05/2026 (1 days after period end); period 01/03/2026-28/05/2026. "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+          <t>Charged 31/01/2026 (29 days before period start); period 01/03/2026-28/05/2026; £0.31. "Door entry SIM card charge"</t>
         </is>
       </c>
     </row>
@@ -11340,30 +11364,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>-7.42</v>
+        <v>5.53</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-7.42 — "E-billing Discount: 29/08/2025 - 28/11/2025"</t>
+          <t>Charged 15/02/2026 (14 days before period start); period 01/03/2026-28/05/2026; £5.53. "Reset fire alarm system"</t>
         </is>
       </c>
     </row>
@@ -11375,12 +11399,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -11390,15 +11414,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Hart Lifts Ltd</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>-1.03</v>
+        <v>4.6</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-1.03 — "Attended site to program numbers as requested"</t>
+          <t>Charged 30/01/2026 (30 days before period start); period 01/03/2026-28/05/2026; £4.60. "Repairs to lift (mis-use)"</t>
         </is>
       </c>
     </row>
@@ -11410,30 +11434,30 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Argyle Locksmiths</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>-7.42</v>
+        <v>2.71</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-7.42 — "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+          <t>Charged 05/02/2026 (24 days before period start); period 01/03/2026-28/05/2026; £2.71. "Lower car park door reset code"</t>
         </is>
       </c>
     </row>
@@ -11445,30 +11469,30 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>-7.72</v>
+        <v>13.2</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-7.72 — "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+          <t>Charged 16/02/2026 (13 days before period start); period 01/03/2026-28/05/2026; £13.20. "Repair to upper car park shutter"</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11504,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11503,7 +11527,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>-7.72 — "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+          <t>Charged 29/05/2026 (1 days after period end); period 01/03/2026-28/05/2026; £-7.72. "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
         </is>
       </c>
     </row>
@@ -11515,23 +11539,30 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Credit / negative line</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HDN- NIG - 2025-2026</t>
-        </is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>-7.42</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>'HDN- NIG - 2025-2026' billed in 2/3 prior quarters but is absent this quarter.</t>
+          <t>-7.42 — "E-billing Discount: 29/08/2025 - 28/11/2025"</t>
         </is>
       </c>
     </row>
@@ -11543,23 +11574,30 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Credit / negative line</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>VWS (UK) T/A Veolia Water Technologies</t>
-        </is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>-1.03</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>'VWS (UK) T/A Veolia Water Technologies' billed in 2/3 prior quarters but is absent this quarter.</t>
+          <t>-1.03 — "Attended site to program numbers as requested"</t>
         </is>
       </c>
     </row>
@@ -11571,35 +11609,196 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-7.42 — "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-7.72 — "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-7.72 — "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>HDN- NIG - 2025-2026</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>'HDN- NIG - 2025-2026' billed in 2/3 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>VWS (UK) T/A Veolia Water Technologies</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>'VWS (UK) T/A Veolia Water Technologies' billed in 2/3 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>Stale service period</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>1883739</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Life System</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="F86" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Service period 01/04/2025-30/04/2025 ends 29 days before the invoice quarter starts (29/05/2025). "Sim card charge for the GSM door access system: 01"</t>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Service period 01/04/2025-30/04/2025 ends 29 days before the invoice quarter starts (29/05/2025); £0.29. "Sim card charge for the GSM door access system: 01"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G81"/>
+  <autoFilter ref="A1:G86"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/.claude/skills/invoice-tracker/output/cost_tracker.xlsx
+++ b/.claude/skills/invoice-tracker/output/cost_tracker.xlsx
@@ -15,8 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anomalies" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Line Items'!$A$1:$O$105</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Anomalies'!$A$1:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Line Items'!$A$1:$O$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Anomalies'!$A$1:$G$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -702,84 +702,123 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>543.16</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>598.58</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>598.58</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
-      <c r="H8" s="5" t="n">
-        <v>2595.07</v>
-      </c>
-      <c r="I8" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n">
+        <v>3193.65</v>
+      </c>
+      <c r="I9" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Totals by tax year (by charge date)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Tax year = UK 6 Apr-5 Apr by default; see Line Items 'Tax year' column.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Tax year</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Total cost</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2023/24</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>326.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024/25</t>
+          <t>2023/24</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>62.44</v>
+        <v>326.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025/26</t>
+          <t>2024/25</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>1814.03</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1826.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>2026/27</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>391.62</v>
+      <c r="B17" s="3" t="n">
+        <v>977.8</v>
       </c>
     </row>
   </sheetData>
@@ -793,7 +832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7782,8 +7821,2323 @@
       </c>
       <c r="O105" t="inlineStr"/>
     </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D106" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="8" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="G106" s="8" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>KC Janitorial Ltd</t>
+        </is>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>Rubbish removal - pump room</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L106" s="9" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="M106" s="8" t="inlineStr"/>
+      <c r="N106" s="8" t="inlineStr"/>
+      <c r="O106" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>KC Janitorial Ltd</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Common Cleaning: 06/05/2026 - 05/08/2026</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="n">
+        <v>1586.22</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="n">
+        <v>45.33</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>05/08/2026</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Ecotricity DD</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Common electricity supply 1: 01/04/2026 - 30/06/2026</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="n">
+        <v>3402.36</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="n">
+        <v>97.20999999999999</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Miscellaneous</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Door entry SIM card charge: 01/07/2026 - 31/07/2026</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>31/07/2026</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D110" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E110" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F110" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G110" s="8" t="inlineStr">
+        <is>
+          <t>01/03/2026</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>Annual monitoring fee PMV</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>294</v>
+      </c>
+      <c r="K110" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L110" s="9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M110" s="8" t="inlineStr"/>
+      <c r="N110" s="8" t="inlineStr"/>
+      <c r="O110" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I111" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly smoke extract sys service</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="K111" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L111" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M111" s="8" t="inlineStr"/>
+      <c r="N111" s="8" t="inlineStr"/>
+      <c r="O111" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D112" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E112" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F112" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G112" s="8" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>Emergency lighting test</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="K112" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L112" s="9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M112" s="8" t="inlineStr"/>
+      <c r="N112" s="8" t="inlineStr"/>
+      <c r="O112" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E113" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="I113" s="8" t="inlineStr">
+        <is>
+          <t>Emergency lighting test</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="K113" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L113" s="9" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="M113" s="8" t="inlineStr"/>
+      <c r="N113" s="8" t="inlineStr"/>
+      <c r="O113" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D114" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E114" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F114" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G114" s="8" t="inlineStr">
+        <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I114" s="8" t="inlineStr">
+        <is>
+          <t>Sim card charge for the GSM door access system</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M114" s="8" t="inlineStr"/>
+      <c r="N114" s="8" t="inlineStr"/>
+      <c r="O114" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D115" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E115" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I115" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly service and inspection of car park ventilation : 01/06/2026 - 01/09/2026</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="K115" s="8" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+      <c r="L115" s="9" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="M115" s="8" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="N115" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="O115" s="8" t="inlineStr">
+        <is>
+          <t>Possible duplicate line (same invoice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F116" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G116" s="8" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I116" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly smoke extract sys service</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>66</v>
+      </c>
+      <c r="K116" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L116" s="9" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M116" s="8" t="inlineStr"/>
+      <c r="N116" s="8" t="inlineStr"/>
+      <c r="O116" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D117" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E117" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly fire alarm service: 03/03/2026 - 11/06/2026</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>189.12</v>
+      </c>
+      <c r="K117" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L117" s="9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M117" s="8" t="inlineStr">
+        <is>
+          <t>03/03/2026</t>
+        </is>
+      </c>
+      <c r="N117" s="8" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="O117" s="8" t="inlineStr">
+        <is>
+          <t>Cross-invoice duplicate charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Chess ICT Ltd</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Lift telephone charges: 01/04/2026 - 30/06/2026</t>
+        </is>
+      </c>
+      <c r="J118" s="3" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>VWS (UK) T/A Veolia Water Technologies</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Technical service agreement: 01/07/2024 - 30/06/2027</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>1/37</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>01/07/2024</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>30/06/2027</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>01/07/2026</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>VWS (UK) T/A Veolia Water Technologies</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Water testing &amp; certification (6 months)</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="n">
+        <v>570</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>1/37</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>PTSG Electrical Services Ltd</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Lightning conductor - Annual test &amp; inspection</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="n">
+        <v>266.4</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>1/37</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>2025/26</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D122" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E122" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G122" s="8" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>Repair/replace lock barrel</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>74.23999999999999</v>
+      </c>
+      <c r="K122" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L122" s="9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M122" s="8" t="inlineStr"/>
+      <c r="N122" s="8" t="inlineStr"/>
+      <c r="O122" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D123" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>Adjusted car park shutter</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="K123" s="8" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+      <c r="L123" s="9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="M123" s="8" t="inlineStr"/>
+      <c r="N123" s="8" t="inlineStr"/>
+      <c r="O123" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D124" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F124" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G124" s="8" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+        </is>
+      </c>
+      <c r="I124" s="8" t="inlineStr">
+        <is>
+          <t>Service checks of 1x booster set</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>216</v>
+      </c>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>1/37</t>
+        </is>
+      </c>
+      <c r="L124" s="9" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="M124" s="8" t="inlineStr"/>
+      <c r="N124" s="8" t="inlineStr"/>
+      <c r="O124" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>Emergency lighting repair</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>483.96</v>
+      </c>
+      <c r="K125" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L125" s="9" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="M125" s="8" t="inlineStr"/>
+      <c r="N125" s="8" t="inlineStr"/>
+      <c r="O125" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D126" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G126" s="8" t="inlineStr">
+        <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="H126" s="8" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>fit lock on cctv cupboard door</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>293.6</v>
+      </c>
+      <c r="K126" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L126" s="9" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="M126" s="8" t="inlineStr"/>
+      <c r="N126" s="8" t="inlineStr"/>
+      <c r="O126" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E127" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>Hart Lifts Ltd</t>
+        </is>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>Loler defect works</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>234</v>
+      </c>
+      <c r="K127" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L127" s="9" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="M127" s="8" t="inlineStr"/>
+      <c r="N127" s="8" t="inlineStr"/>
+      <c r="O127" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Staple fit new padlock</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="n">
+        <v>130</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Repair lock on upper car park door, replace latch</t>
+        </is>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Martyn Reid Property Maintenance</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Mastic repairs to open joint on cladding</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>630</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>1/37</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>17.03</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>To attend site regarding report that the lower car park lights weren't staying on long enough after being activated, increased time on the PIR sensors as required</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Attended site and found the CCTV dead, the power supply and monitor require replacement (quote to follow)</t>
+        </is>
+      </c>
+      <c r="J132" s="3" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Attended site and replaced 2x rim units, programmed and tested</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>334.2</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E134" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F134" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="G134" s="8" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>Sim card charge for the GSM door access system</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="K134" s="8" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L134" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="M134" s="8" t="inlineStr"/>
+      <c r="N134" s="8" t="inlineStr"/>
+      <c r="O134" s="8" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Door entry sim card change: 01/06/2026 - 30/06/2026</t>
+        </is>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>1/35</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F136" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="G136" s="8" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="H136" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly service and inspection of car park shutter (lower) : 01/06/2026 - 01/09/2026</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>260.04</v>
+      </c>
+      <c r="K136" s="8" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+      <c r="L136" s="9" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="M136" s="8" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="N136" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="O136" s="8" t="inlineStr">
+        <is>
+          <t>Possible duplicate line (same invoice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E137" s="8" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr">
+        <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>Quarterly service and inspection of the car park shutter (upper) : 01/06/2026 - 01/09/2026</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>260.04</v>
+      </c>
+      <c r="K137" s="8" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+      <c r="L137" s="9" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="M137" s="8" t="inlineStr">
+        <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="N137" s="8" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="O137" s="8" t="inlineStr">
+        <is>
+          <t>Possible duplicate line (same invoice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="10" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C138" s="10" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D138" s="10" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E138" s="10" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F138" s="10" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>E-billing Discount: 29/08/2026 - 28/11/2026</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="K138" s="10" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="L138" s="11" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="M138" s="10" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="N138" s="10" t="inlineStr">
+        <is>
+          <t>28/11/2026</t>
+        </is>
+      </c>
+      <c r="O138" s="10" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Management Fee: 29/08/2026 - 28/11/2026</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>29/08/2026</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>28/11/2026</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>28/08/2026</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>DAWN- INTACT-26-27</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Quarterly buildings insurance: 26/08/2026 - 25/11/2026</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="n">
+        <v>181.01</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="n">
+        <v>181.01</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>26/08/2026</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>25/11/2026</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O105"/>
+  <autoFilter ref="A1:O140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7794,7 +10148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7803,6 +10157,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7837,6 +10192,12 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>2060244
+28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
@@ -7860,7 +10221,10 @@
         <v>45.33</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>185.09</v>
+        <v>50.48</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>235.57</v>
       </c>
     </row>
     <row r="3">
@@ -7882,7 +10246,10 @@
         <v>84.61</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>700.29</v>
+        <v>97.20999999999999</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>797.5</v>
       </c>
     </row>
     <row r="4">
@@ -7904,6 +10271,9 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
         <v>8.49</v>
       </c>
     </row>
@@ -7926,7 +10296,10 @@
         <v>181.01</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>719.8099999999999</v>
+        <v>181.01</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>900.8200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -7948,7 +10321,10 @@
         <v>61.55</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>223.77</v>
+        <v>71.48</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>295.25</v>
       </c>
     </row>
     <row r="7">
@@ -7970,6 +10346,9 @@
         <v>15.04</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>35.76</v>
       </c>
     </row>
@@ -7992,7 +10371,10 @@
         <v>14.06</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>38.48</v>
+        <v>29.69</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>68.17</v>
       </c>
     </row>
     <row r="9">
@@ -8014,7 +10396,10 @@
         <v>78.78</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>303.28</v>
+        <v>78.78</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>382.06</v>
       </c>
     </row>
     <row r="10">
@@ -8036,7 +10421,10 @@
         <v>0.62</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.62</v>
+        <v>0.36</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="11">
@@ -8058,7 +10446,10 @@
         <v>89.84999999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>379.48</v>
+        <v>89.56999999999999</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>469.05</v>
       </c>
     </row>
     <row r="12">
@@ -8080,7 +10471,10 @@
         <v>570.85</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2595.07</v>
+        <v>598.58</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>3193.65</v>
       </c>
     </row>
   </sheetData>
@@ -8094,7 +10488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8103,6 +10497,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8137,6 +10532,12 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
+          <t>2060244
+28/08/2026</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
           <t>Total</t>
         </is>
       </c>
@@ -8160,6 +10561,9 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n">
         <v>22.29</v>
       </c>
     </row>
@@ -8182,6 +10586,9 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="n">
         <v>10.51</v>
       </c>
     </row>
@@ -8204,7 +10611,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>71.42</v>
+        <v>24.6</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>96.02</v>
       </c>
     </row>
     <row r="5">
@@ -8226,7 +10636,10 @@
         <v>2.71</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.71</v>
+        <v>15.53</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>18.24</v>
       </c>
     </row>
     <row r="6">
@@ -8248,7 +10661,10 @@
         <v>3.04</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>16.24</v>
+        <v>5.24</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>21.48</v>
       </c>
     </row>
     <row r="7">
@@ -8270,6 +10686,9 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>3.34</v>
       </c>
     </row>
@@ -8292,6 +10711,9 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
         <v>5.15</v>
       </c>
     </row>
@@ -8314,6 +10736,9 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
         <v>18.85</v>
       </c>
     </row>
@@ -8336,6 +10761,9 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>11.43</v>
       </c>
     </row>
@@ -8358,7 +10786,10 @@
         <v>181.01</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>362.02</v>
+        <v>181.01</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>543.03</v>
       </c>
     </row>
     <row r="12">
@@ -8380,7 +10811,10 @@
         <v>84.61</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>373.31</v>
+        <v>97.20999999999999</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>470.52</v>
       </c>
     </row>
     <row r="13">
@@ -8402,6 +10836,9 @@
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
         <v>346.36</v>
       </c>
     </row>
@@ -8424,7 +10861,10 @@
         <v>19.64</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>53.09</v>
+        <v>6.68</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>59.77</v>
       </c>
     </row>
     <row r="15">
@@ -8446,6 +10886,9 @@
         <v>5.51</v>
       </c>
       <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
         <v>10.31</v>
       </c>
     </row>
@@ -8468,6 +10911,9 @@
         <v>0</v>
       </c>
       <c r="F16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>3.77</v>
       </c>
     </row>
@@ -8490,183 +10936,235 @@
         <v>45.33</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>181.32</v>
+        <v>50.48</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>231.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Martyn Reid Property Maintenance</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>72.86</v>
+        <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>71.83</v>
+        <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>78.78</v>
+        <v>0</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>78.78</v>
+        <v>0</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>302.25</v>
+        <v>17.03</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>17.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ONESCO Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0</v>
+        <v>72.86</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>44.27</v>
+        <v>71.83</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0</v>
+        <v>78.78</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>0</v>
+        <v>78.78</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>44.27</v>
+        <v>78.78</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>381.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>ONESCO Ltd</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>55.2</v>
+        <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>32.24</v>
+        <v>44.27</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>29.51</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>81.91</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>198.86</v>
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>44.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PTSG Electrical Services Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>55.2</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>22.94</v>
+        <v>32.24</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>29.51</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>9.73</v>
+        <v>81.91</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>32.67</v>
+        <v>78.17</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>277.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+          <t>PTSG Electrical Services Ltd</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>101.82</v>
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>5.83</v>
-      </c>
       <c r="E22" s="3" t="n">
-        <v>58.58</v>
+        <v>9.73</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>166.23</v>
+        <v>7.2</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>39.87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SSE Scottish Hydro - A/C 00000000</t>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>326.98</v>
+        <v>101.82</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0</v>
+        <v>58.58</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>326.98</v>
+        <v>5.83</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>172.06</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>VWS (UK) T/A Veolia Water Technologies</t>
+          <t>SSE Scottish Hydro - A/C 00000000</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>16.28</v>
+        <v>326.98</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>15.41</v>
+        <v>0</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>31.69</v>
+        <v>0</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>326.98</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VWS (UK) T/A Veolia Water Technologies</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>15.41</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>62.51</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B26" s="5" t="n">
         <v>903.53</v>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C26" s="5" t="n">
         <v>597.3099999999999</v>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D26" s="5" t="n">
         <v>523.38</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E26" s="5" t="n">
         <v>570.85</v>
       </c>
-      <c r="F25" s="5" t="n">
-        <v>2595.07</v>
+      <c r="F26" s="5" t="n">
+        <v>598.58</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>3193.65</v>
       </c>
     </row>
   </sheetData>
@@ -8739,10 +11237,10 @@
         <v>139.76</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>45.33</v>
+        <v>95.81</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>185.09</v>
+        <v>235.57</v>
       </c>
     </row>
     <row r="3">
@@ -8761,10 +11259,10 @@
         <v>373.31</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>700.29</v>
+        <v>797.5</v>
       </c>
     </row>
     <row r="4">
@@ -8805,10 +11303,10 @@
         <v>538.8</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>181.01</v>
+        <v>362.02</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>719.8099999999999</v>
+        <v>900.8200000000001</v>
       </c>
     </row>
     <row r="6">
@@ -8824,13 +11322,13 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>223.77</v>
+        <v>234.05</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>61.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>223.77</v>
+        <v>295.25</v>
       </c>
     </row>
     <row r="7">
@@ -8871,10 +11369,10 @@
         <v>38.48</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>0</v>
+        <v>29.69</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>38.48</v>
+        <v>68.17</v>
       </c>
     </row>
     <row r="9">
@@ -8893,10 +11391,10 @@
         <v>138</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>165.28</v>
+        <v>244.06</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>303.28</v>
+        <v>382.06</v>
       </c>
     </row>
     <row r="10">
@@ -8915,10 +11413,10 @@
         <v>0.62</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.62</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="11">
@@ -8934,13 +11432,13 @@
         <v>62.44</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>317.04</v>
+        <v>319.16</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>87.45</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>379.48</v>
+        <v>469.05</v>
       </c>
     </row>
     <row r="12">
@@ -8956,13 +11454,13 @@
         <v>62.44</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1814.03</v>
+        <v>1826.43</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>391.62</v>
+        <v>977.8</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>2595.07</v>
+        <v>3193.65</v>
       </c>
     </row>
   </sheetData>
@@ -8976,7 +11474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -9208,61 +11706,65 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>Possible duplicate line (same invoice)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2x same vendor/period/cost with different descriptions: PTM Security Solutions Ltd 01/06/2026-01/09/2026 14.45 each — "Quarterly service and inspection of car " | "Quarterly service and inspection of the "</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Stale service period</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>1883739</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SSE Scottish Hydro - A/C 00000000</t>
         </is>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>326.98</v>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Service period 12/10/2023-31/01/2024 ends 484 days before the invoice quarter starts (29/05/2025); £326.98. "Common electricity supply : 12/10/2023 - 31/01/202"</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="3" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Maintenance: 20.40 this quarter vs prior average 4.02 (5.1x, higher).</t>
         </is>
       </c>
     </row>
@@ -9274,30 +11776,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" s="3" t="n">
-        <v>13.85</v>
+        <v>16.38</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Charged 23/04/2025 (36 days before period start); period 29/05/2025-28/08/2025; £13.85. "Attended site to re-fit fan control cabinet to the wall: 26/"</t>
+          <t>Maintenance: 20.40 this quarter vs prior average 4.02 (5.1x, higher).</t>
         </is>
       </c>
     </row>
@@ -9309,30 +11807,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2060244</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" s="3" t="n">
-        <v>-1.03</v>
+        <v>16.86333333333334</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Charged 01/07/2025 (59 days before period start); period 29/08/2025-28/11/2025; £-1.03. "Attended site to program numbers as requested"</t>
+          <t>Maintenance: 29.69 this quarter vs prior average 12.83 (2.3x, higher).</t>
         </is>
       </c>
     </row>
@@ -9349,7 +11843,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9363,11 +11857,11 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.4</v>
+        <v>13.85</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Charged 15/07/2025 (45 days before period start); period 29/08/2025-28/11/2025; £3.40. "Monitoring of CCTV"</t>
+          <t>Charged 23/04/2025 (36 days before period start); period 29/05/2025-28/08/2025; £13.85. "Attended site to re-fit fan control cabinet to the wall: 26/"</t>
         </is>
       </c>
     </row>
@@ -9394,15 +11888,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ONESCO Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>11.03</v>
+        <v>-1.03</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Charged 17/07/2025 (43 days before period start); period 29/08/2025-28/11/2025; £11.03. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2025"</t>
+          <t>Charged 01/07/2025 (59 days before period start); period 29/08/2025-28/11/2025; £-1.03. "Attended site to program numbers as requested"</t>
         </is>
       </c>
     </row>
@@ -9419,25 +11913,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>86.5</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Charged 28/05/2026 (89 days after period end); period 29/11/2025-28/02/2026; £86.50. "Management Fee: 01/03/2026 - 28/05/2026"</t>
+          <t>Charged 15/07/2025 (45 days before period start); period 29/08/2025-28/11/2025; £3.40. "Monitoring of CCTV"</t>
         </is>
       </c>
     </row>
@@ -9454,25 +11948,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>ONESCO Ltd</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>2.7</v>
+        <v>11.03</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Charged 17/12/2025 (74 days before period start); period 01/03/2026-28/05/2026; £2.70. "Quarterly fire alarm service"</t>
+          <t>Charged 17/07/2025 (43 days before period start); period 29/08/2025-28/11/2025; £11.03. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2025"</t>
         </is>
       </c>
     </row>
@@ -9489,25 +11983,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.03</v>
+        <v>86.5</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Charged 23/12/2025 (68 days before period start); period 01/03/2026-28/05/2026; £1.03. "Door entry sim card change"</t>
+          <t>Charged 28/05/2026 (89 days after period end); period 29/11/2025-28/02/2026; £86.50. "Management Fee: 01/03/2026 - 28/05/2026"</t>
         </is>
       </c>
     </row>
@@ -9529,20 +12023,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>58.58</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Charged 28/01/2026 (32 days before period start); period 01/03/2026-28/05/2026; £58.58. "Attended site to install new pump to replace missing pump"</t>
+          <t>Charged 17/12/2025 (74 days before period start); period 01/03/2026-28/05/2026; £2.70. "Quarterly fire alarm service"</t>
         </is>
       </c>
     </row>
@@ -9564,20 +12058,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>86.5</v>
+        <v>1.03</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Charged 28/08/2026 (92 days after period end); period 01/03/2026-28/05/2026; £86.50. "Management Fee: 29/05/2026 - 28/08/2026"</t>
+          <t>Charged 23/12/2025 (68 days before period start); period 01/03/2026-28/05/2026; £1.03. "Door entry sim card change"</t>
         </is>
       </c>
     </row>
@@ -9589,30 +12083,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cross-invoice duplicate charge</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ecotricity DD</t>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>144.38</v>
+        <v>58.58</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ecotricity DD: service 01/04/2025-01/10/2025 overlaps 92d with inv 1883739 15/03/2025-01/07/2025; £144.38. "Common electricity supply 1: 01/04/2025 " vs "Common electricity supply 1: 15/03/2025 "</t>
+          <t>Charged 28/01/2026 (32 days before period start); period 01/03/2026-28/05/2026; £58.58. "Attended site to install new pump to replace missing pump"</t>
         </is>
       </c>
     </row>
@@ -9624,30 +12118,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cross-invoice duplicate charge</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>5.23</v>
+        <v>86.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd: service 01/06/2025-30/09/2025 overlaps 36d with inv 1883739 26/06/2025-31/07/2025; £5.23. "Quarterly service and inspection of car " vs "Door entry SIM card charge: 26/06/2025 -"</t>
+          <t>Charged 28/08/2026 (92 days after period end); period 01/03/2026-28/05/2026; £86.50. "Management Fee: 29/05/2026 - 28/08/2026"</t>
         </is>
       </c>
     </row>
@@ -9659,12 +12153,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cross-invoice duplicate charge</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2060244</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -9678,11 +12172,11 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>5.23</v>
+        <v>8.4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd: service 01/06/2025-30/09/2025 overlaps 122d with inv 1883739 01/06/2025-30/09/2025; £5.23. "Quarterly service and inspection of car " vs "Quarterly service and inspection car par"</t>
+          <t>Charged 01/03/2026 (89 days before period start); period 29/05/2026-28/08/2026; £8.40. "Annual monitoring fee PMV"</t>
         </is>
       </c>
     </row>
@@ -9694,30 +12188,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cross-invoice duplicate charge</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>2060244</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electricity</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ecotricity DD</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>98.59</v>
+        <v>1.88</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ecotricity DD: service 01/06/2025-01/01/2026 overlaps 123d with inv 1933254 01/04/2025-01/10/2025; £98.59. "Common electricity supply 1: 01/06/2025 " vs "Common electricity supply 1: 01/04/2025 "</t>
+          <t>Charged 03/03/2026 (87 days before period start); period 29/05/2026-28/08/2026; £1.88. "Quarterly smoke extract sys service"</t>
         </is>
       </c>
     </row>
@@ -9729,23 +12223,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HDN- NIG - 2025-2026</t>
-        </is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2.12</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>'HDN- NIG - 2025-2026' billed in 2/2 prior quarters but is absent this quarter.</t>
+          <t>Charged 20/02/2026 (98 days before period start); period 29/05/2026-28/08/2026; £2.12. "Repair/replace lock barrel"</t>
         </is>
       </c>
     </row>
@@ -9757,23 +12258,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ASD Electrical Contractors Ltd</t>
-        </is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>9.9</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>'ASD Electrical Contractors Ltd' billed in 3/3 prior quarters but is absent this quarter.</t>
+          <t>Charged 15/04/2026 (44 days before period start); period 29/05/2026-28/08/2026; £9.90. "Adjusted car park shutter"</t>
         </is>
       </c>
     </row>
@@ -9785,7 +12293,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9793,18 +12301,22 @@
           <t>1933254</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AB Decorators</t>
+          <t>Ecotricity DD</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>22.29</v>
+        <v>144.38</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>'AB Decorators' appears this quarter but not in any prior quarter (cost 22.29).</t>
+          <t>Ecotricity DD: service 01/04/2025-01/10/2025 overlaps 92d with inv 1883739 15/03/2025-01/07/2025; £144.38. "Common electricity supply 1: 01/04/2025 " vs "Common electricity supply 1: 15/03/2025 "</t>
         </is>
       </c>
     </row>
@@ -9816,7 +12328,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9824,18 +12336,22 @@
           <t>1933254</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Columbus Facilities Maintenance Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>18.85</v>
+        <v>5.23</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>'Columbus Facilities Maintenance Ltd' appears this quarter but not in any prior quarter (cost 18.85).</t>
+          <t>PTM Security Solutions Ltd: service 01/06/2025-30/09/2025 overlaps 36d with inv 1883739 26/06/2025-31/07/2025; £5.23. "Quarterly service and inspection of car " vs "Door entry SIM card charge: 26/06/2025 -"</t>
         </is>
       </c>
     </row>
@@ -9847,7 +12363,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9855,18 +12371,22 @@
           <t>1933254</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hart Lifts Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>7.52</v>
+        <v>5.23</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>'Hart Lifts Ltd' appears this quarter but not in any prior quarter (cost 7.52).</t>
+          <t>PTM Security Solutions Ltd: service 01/06/2025-30/09/2025 overlaps 122d with inv 1883739 01/06/2025-30/09/2025; £5.23. "Quarterly service and inspection of car " vs "Quarterly service and inspection car par"</t>
         </is>
       </c>
     </row>
@@ -9878,26 +12398,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Electricity</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Integra Building Solutions Ltd</t>
+          <t>Ecotricity DD</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2.23</v>
+        <v>98.59</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>'Integra Building Solutions Ltd' appears this quarter but not in any prior quarter (cost 2.23).</t>
+          <t>Ecotricity DD: service 01/06/2025-01/01/2026 overlaps 123d with inv 1933254 01/04/2025-01/10/2025; £98.59. "Common electricity supply 1: 01/06/2025 " vs "Common electricity supply 1: 01/04/2025 "</t>
         </is>
       </c>
     </row>
@@ -9909,26 +12433,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Cross-invoice duplicate charge</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ONESCO Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>44.27</v>
+        <v>5.4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>'ONESCO Ltd' appears this quarter but not in any prior quarter (cost 44.27).</t>
+          <t>PTM Security Solutions Ltd: service 03/03/2026-11/06/2026 overlaps 22d with inv 2013624 28/02/2026-24/03/2026; £5.40. "Quarterly fire alarm service: 03/03/2026" vs "Door entry SIM card charge: 28/02/2026 -"</t>
         </is>
       </c>
     </row>
@@ -9940,26 +12468,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Dropped vendor</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PTSG Electrical Services Ltd</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>22.94</v>
+          <t>HDN- NIG - 2025-2026</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>'PTSG Electrical Services Ltd' appears this quarter but not in any prior quarter (cost 22.94).</t>
+          <t>'HDN- NIG - 2025-2026' billed in 2/2 prior quarters but is absent this quarter.</t>
         </is>
       </c>
     </row>
@@ -9971,26 +12496,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New vendor</t>
+          <t>Dropped vendor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>APS Safety Systems Limited</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>10.51</v>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>'APS Safety Systems Limited' appears this quarter but not in any prior quarter (cost 10.51).</t>
+          <t>'ASD Electrical Contractors Ltd' billed in 3/3 prior quarters but is absent this quarter.</t>
         </is>
       </c>
     </row>
@@ -10007,21 +12529,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>City Drain Clear</t>
+          <t>AB Decorators</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>3.34</v>
+        <v>22.29</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>'City Drain Clear' appears this quarter but not in any prior quarter (cost 3.34).</t>
+          <t>'AB Decorators' appears this quarter but not in any prior quarter (cost 22.29).</t>
         </is>
       </c>
     </row>
@@ -10038,21 +12560,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cleansite Solutions Ltd</t>
+          <t>Columbus Facilities Maintenance Ltd</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>5.15</v>
+        <v>18.85</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>'Cleansite Solutions Ltd' appears this quarter but not in any prior quarter (cost 5.15).</t>
+          <t>'Columbus Facilities Maintenance Ltd' appears this quarter but not in any prior quarter (cost 18.85).</t>
         </is>
       </c>
     </row>
@@ -10069,21 +12591,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DAWN ZURICH 26/27</t>
+          <t>Hart Lifts Ltd</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>11.43</v>
+        <v>7.52</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>'DAWN ZURICH 26/27' appears this quarter but not in any prior quarter (cost 11.43).</t>
+          <t>'Hart Lifts Ltd' appears this quarter but not in any prior quarter (cost 7.52).</t>
         </is>
       </c>
     </row>
@@ -10100,21 +12622,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DAWN- INTACT-26-27</t>
+          <t>Integra Building Solutions Ltd</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>181.01</v>
+        <v>2.23</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>'DAWN- INTACT-26-27' appears this quarter but not in any prior quarter (cost 181.01).</t>
+          <t>'Integra Building Solutions Ltd' appears this quarter but not in any prior quarter (cost 2.23).</t>
         </is>
       </c>
     </row>
@@ -10131,21 +12653,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>J.T. Mullen Building Services</t>
+          <t>ONESCO Ltd</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>3.77</v>
+        <v>44.27</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>'J.T. Mullen Building Services' appears this quarter but not in any prior quarter (cost 3.77).</t>
+          <t>'ONESCO Ltd' appears this quarter but not in any prior quarter (cost 44.27).</t>
         </is>
       </c>
     </row>
@@ -10162,21 +12684,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Argyle Locksmiths</t>
+          <t>PTSG Electrical Services Ltd</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.71</v>
+        <v>22.94</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>'Argyle Locksmiths' appears this quarter but not in any prior quarter (cost 2.71).</t>
+          <t>'PTSG Electrical Services Ltd' appears this quarter but not in any prior quarter (cost 22.94).</t>
         </is>
       </c>
     </row>
@@ -10188,23 +12710,26 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>APS Safety Systems Limited</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>10.51</v>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>'attended site and downloaded cctv footage from mailbox camera' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'APS Safety Systems Limited' appears this quarter but not in any prior quarter (cost 10.51).</t>
         </is>
       </c>
     </row>
@@ -10216,23 +12741,26 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>City Drain Clear</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>3.34</v>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>'attended site and removed snib from fire door dry riser door was detached from wall so attached timber batons to secure door' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'City Drain Clear' appears this quarter but not in any prior quarter (cost 3.34).</t>
         </is>
       </c>
     </row>
@@ -10244,23 +12772,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cleansite Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>5.15</v>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>'attended site to re fit fan control cabinet to the wall' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'Cleansite Solutions Ltd' appears this quarter but not in any prior quarter (cost 5.15).</t>
         </is>
       </c>
     </row>
@@ -10272,23 +12803,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>DAWN ZURICH 26/27</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>11.43</v>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>'emergency lighting repair' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'DAWN ZURICH 26/27' appears this quarter but not in any prior quarter (cost 11.43).</t>
         </is>
       </c>
     </row>
@@ -10300,23 +12834,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>DAWN- INTACT-26-27</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>181.01</v>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>'quarterly service and inspection car park garage shutter' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'DAWN- INTACT-26-27' appears this quarter but not in any prior quarter (cost 181.01).</t>
         </is>
       </c>
     </row>
@@ -10328,23 +12865,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>J.T. Mullen Building Services</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>3.77</v>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>'replace faulty ball valves' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'J.T. Mullen Building Services' appears this quarter but not in any prior quarter (cost 3.77).</t>
         </is>
       </c>
     </row>
@@ -10356,23 +12896,26 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2.71</v>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>'service checks of x booster set' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'Argyle Locksmiths' appears this quarter but not in any prior quarter (cost 2.71).</t>
         </is>
       </c>
     </row>
@@ -10384,23 +12927,26 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Recurring item missing</t>
+          <t>New vendor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Martyn Reid Property Maintenance</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>17.03</v>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>'sim card charge for the gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'Martyn Reid Property Maintenance' appears this quarter but not in any prior quarter (cost 17.03).</t>
         </is>
       </c>
     </row>
@@ -10428,7 +12974,7 @@
       <c r="E45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>'sim card charges for gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'attended site and downloaded cctv footage from mailbox camera' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10456,7 +13002,7 @@
       <c r="E46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>'vecon drive at pump' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'attended site and removed snib from fire door dry riser door was detached from wall so attached timber batons to secure door' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10478,13 +13024,13 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>'water testing certification' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+          <t>'attended site to re fit fan control cabinet to the wall' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10501,18 +13047,18 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>'attended site to program numbers as requested' (e.g. Repairs) appeared in all 2 prior quarters but not this quarter.</t>
+          <t>'emergency lighting repair' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10529,18 +13075,18 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>'quarterly fire alarm service' (e.g. Life System) appeared in all 2 prior quarters but not this quarter.</t>
+          <t>'quarterly service and inspection car park garage shutter' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10552,12 +13098,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stale service period</t>
+          <t>Recurring item missing</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10565,17 +13111,10 @@
           <t>Repairs</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>13.85</v>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Service period 26/03/2025-23/04/2025 ends 36 days before the invoice quarter starts (29/05/2025); £13.85. "Attended site to re-fit fan control cabinet to the"</t>
+          <t>'replace faulty ball valves' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
         </is>
       </c>
     </row>
@@ -10587,282 +13126,261 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>'service checks of x booster set' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>'sim card charge for the gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>'sim card charges for gsm door access system' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>'vecon drive at pump' (e.g. Repairs) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>'water testing certification' (e.g. Life System) appeared in all 1 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>'attended site to program numbers as requested' (e.g. Repairs) appeared in all 2 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Recurring item missing</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>'quarterly fire alarm service' (e.g. Life System) appeared in all 2 prior quarters but not this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>Stale service period</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>13.85</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Service period 26/03/2025-23/04/2025 ends 36 days before the invoice quarter starts (29/05/2025); £13.85. "Attended site to re-fit fan control cabinet to the"</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Stale service period</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
         <is>
           <t>1933254</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Repairs</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>ONESCO Ltd</t>
         </is>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="F59" s="3" t="n">
         <v>11.03</v>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Service period 26/06/2025-17/07/2025 ends 43 days before the invoice quarter starts (29/08/2025); £11.03. "Trace &amp; locate water ingress: 26/06/2025 - 17/07/2"</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" s="3" t="n">
-        <v>-228.33</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Electricity: 144.38 this quarter vs prior average 372.71 (0.4x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" s="3" t="n">
-        <v>-159.955</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Electricity: 98.59 this quarter vs prior average 258.54 (0.4x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" s="3" t="n">
-        <v>-35.585</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Life System: 30.35 this quarter vs prior average 65.94 (0.5x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" s="3" t="n">
-        <v>-77.255</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Repairs: 45.04 this quarter vs prior average 122.30 (0.4x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Abnormal category total</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Electricity</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" s="3" t="n">
-        <v>-120.6166666666667</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Electricity: 84.61 this quarter vs prior average 205.23 (0.4x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Abnormal vendor total</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ASD Electrical Contractors Ltd</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>-32.32</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>ASD Electrical Contractors Ltd: 2.26 this quarter vs prior average 34.58 (0.1x, lower).</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Abnormal vendor total</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2013624</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>42.92666666666666</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd: 81.91 this quarter vs prior average 38.98 (2.1x, higher).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Charge date outside invoice period</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1883739</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Charged 30/04/2025 (29 days before period start); period 29/05/2025-28/08/2025; £0.29. "Sim card charge for the GSM door access system: 01/04/2025 -"</t>
         </is>
       </c>
     </row>
@@ -10874,30 +13392,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" s="3" t="n">
-        <v>4.25</v>
+        <v>-228.33</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Charged 23/05/2025 (6 days before period start); period 29/05/2025-28/08/2025; £4.25. "Attended site and downloaded CCTV footage from mailbox camer"</t>
+          <t>Electricity: 144.38 this quarter vs prior average 372.71 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10909,30 +13423,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Newton Property Management Ltd</t>
-        </is>
-      </c>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" s="3" t="n">
-        <v>80.28</v>
+        <v>-159.955</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Charged 29/08/2025 (1 days after period end); period 29/05/2025-28/08/2025; £80.28. "Management Fee: 29/08/2025 - 28/11/2025"</t>
+          <t>Electricity: 98.59 this quarter vs prior average 258.54 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -10944,12 +13454,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10957,17 +13467,13 @@
           <t>Life System</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>PTSG Electrical Services Ltd</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" s="3" t="n">
-        <v>7.2</v>
+        <v>-35.585</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Charged 08/08/2025 (21 days before period start); period 29/08/2025-28/11/2025; £7.20. "Test &amp; Inspection of the Lighting Protection System"</t>
+          <t>Life System: 30.35 this quarter vs prior average 65.94 (0.5x, lower).</t>
         </is>
       </c>
     </row>
@@ -10979,30 +13485,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Life System</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>PTM Security Solutions Ltd</t>
-        </is>
-      </c>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" s="3" t="n">
-        <v>0.3</v>
+        <v>-77.255</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Charged 22/08/2025 (7 days before period start); period 29/08/2025-28/11/2025; £0.30. "Door entry SIM card charge"</t>
+          <t>Repairs: 45.04 this quarter vs prior average 122.30 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -11014,30 +13516,26 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal category total</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>2013624</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Repairs</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AB Decorators</t>
-        </is>
-      </c>
+          <t>Electricity</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" s="3" t="n">
-        <v>22.29</v>
+        <v>-120.6166666666667</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Charged 26/08/2025 (3 days before period start); period 29/08/2025-28/11/2025; £22.29. "Repairs to floor 11, 4, 1 &amp; stairwell to ground"</t>
+          <t>Electricity: 84.61 this quarter vs prior average 205.23 (0.4x, lower).</t>
         </is>
       </c>
     </row>
@@ -11049,30 +13547,26 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal vendor total</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>ASD Electrical Contractors Ltd</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>-7.42</v>
+        <v>-32.32</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025; £-7.42. "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+          <t>ASD Electrical Contractors Ltd: 2.26 this quarter vs prior average 34.58 (0.1x, lower).</t>
         </is>
       </c>
     </row>
@@ -11084,30 +13578,26 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal vendor total</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1933254</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Management Fee</t>
-        </is>
-      </c>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>80.28</v>
+        <v>42.92666666666666</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025; £80.28. "Management Fee: 29/11/2025 - 28/02/2026"</t>
+          <t>PTM Security Solutions Ltd: 81.91 this quarter vs prior average 38.98 (2.1x, higher).</t>
         </is>
       </c>
     </row>
@@ -11119,30 +13609,26 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal vendor total</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Grounds</t>
-        </is>
-      </c>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cleansite Solutions Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>5.15</v>
+        <v>28.455</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Charged 17/11/2025 (12 days before period start); period 29/11/2025-28/02/2026; £5.15. "Bulk uplift"</t>
+          <t>PTM Security Solutions Ltd: 78.17 this quarter vs prior average 49.72 (1.6x, higher).</t>
         </is>
       </c>
     </row>
@@ -11154,30 +13640,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Charge date outside invoice period</t>
+          <t>Abnormal vendor total</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1968807</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Repairs</t>
-        </is>
-      </c>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Ritchie Mackenzie &amp; Co Ltd</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>5.83</v>
+        <v>-49.58</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Charged 31/10/2025 (29 days before period start); period 29/11/2025-28/02/2026; £5.83. "Service checks on 1 x Two Pump Booster Set"</t>
+          <t>Ritchie Mackenzie &amp; Co Ltd: 5.83 this quarter vs prior average 55.41 (0.1x, lower).</t>
         </is>
       </c>
     </row>
@@ -11194,25 +13676,25 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hart Lifts Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>8.33</v>
+        <v>0.29</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Charged 14/11/2025 (15 days before period start); period 29/11/2025-28/02/2026; £8.33. "Repairs to lift controller unit"</t>
+          <t>Charged 30/04/2025 (29 days before period start); period 29/05/2025-28/08/2025; £0.29. "Sim card charge for the GSM door access system: 01/04/2025 -"</t>
         </is>
       </c>
     </row>
@@ -11229,25 +13711,25 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hart Lifts Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>5.48</v>
+        <v>4.25</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Charged 21/11/2025 (8 days before period start); period 29/11/2025-28/02/2026; £5.48. "Renewed damaged lift door spring"</t>
+          <t>Charged 23/05/2025 (6 days before period start); period 29/05/2025-28/08/2025; £4.25. "Attended site and downloaded CCTV footage from mailbox camer"</t>
         </is>
       </c>
     </row>
@@ -11264,25 +13746,25 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1883739</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Integra Building Solutions Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>2.57</v>
+        <v>80.28</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Charged 25/11/2025 (4 days before period start); period 29/11/2025-28/02/2026; £2.57. "Replace dry riser inlet lock"</t>
+          <t>Charged 29/08/2025 (1 days after period end); period 29/05/2025-28/08/2025; £80.28. "Management Fee: 29/08/2025 - 28/11/2025"</t>
         </is>
       </c>
     </row>
@@ -11299,25 +13781,25 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1968807</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTSG Electrical Services Ltd</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>-7.72</v>
+        <v>7.2</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Charged 01/03/2026 (1 days after period end); period 29/11/2025-28/02/2026; £-7.72. "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+          <t>Charged 08/08/2025 (21 days before period start); period 29/08/2025-28/11/2025; £7.20. "Test &amp; Inspection of the Lighting Protection System"</t>
         </is>
       </c>
     </row>
@@ -11334,7 +13816,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -11348,11 +13830,11 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Charged 31/01/2026 (29 days before period start); period 01/03/2026-28/05/2026; £0.31. "Door entry SIM card charge"</t>
+          <t>Charged 22/08/2025 (7 days before period start); period 29/08/2025-28/11/2025; £0.30. "Door entry SIM card charge"</t>
         </is>
       </c>
     </row>
@@ -11369,25 +13851,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Life System</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>AB Decorators</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>5.53</v>
+        <v>22.29</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Charged 15/02/2026 (14 days before period start); period 01/03/2026-28/05/2026; £5.53. "Reset fire alarm system"</t>
+          <t>Charged 26/08/2025 (3 days before period start); period 29/08/2025-28/11/2025; £22.29. "Repairs to floor 11, 4, 1 &amp; stairwell to ground"</t>
         </is>
       </c>
     </row>
@@ -11404,25 +13886,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hart Lifts Ltd</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>4.6</v>
+        <v>-7.42</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Charged 30/01/2026 (30 days before period start); period 01/03/2026-28/05/2026; £4.60. "Repairs to lift (mis-use)"</t>
+          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025; £-7.42. "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
         </is>
       </c>
     </row>
@@ -11439,25 +13921,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1933254</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Management Fee</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Argyle Locksmiths</t>
+          <t>Newton Property Management Ltd</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>2.71</v>
+        <v>80.28</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Charged 05/02/2026 (24 days before period start); period 01/03/2026-28/05/2026; £2.71. "Lower car park door reset code"</t>
+          <t>Charged 29/11/2025 (1 days after period end); period 29/08/2025-28/11/2025; £80.28. "Management Fee: 29/11/2025 - 28/02/2026"</t>
         </is>
       </c>
     </row>
@@ -11474,25 +13956,25 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Repairs</t>
+          <t>Grounds</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>PTM Security Solutions Ltd</t>
+          <t>Cleansite Solutions Ltd</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>13.2</v>
+        <v>5.15</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Charged 16/02/2026 (13 days before period start); period 01/03/2026-28/05/2026; £13.20. "Repair to upper car park shutter"</t>
+          <t>Charged 17/11/2025 (12 days before period start); period 29/11/2025-28/02/2026; £5.15. "Bulk uplift"</t>
         </is>
       </c>
     </row>
@@ -11509,25 +13991,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2013624</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>-7.72</v>
+        <v>5.83</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Charged 29/05/2026 (1 days after period end); period 01/03/2026-28/05/2026; £-7.72. "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+          <t>Charged 31/10/2025 (29 days before period start); period 29/11/2025-28/02/2026; £5.83. "Service checks on 1 x Two Pump Booster Set"</t>
         </is>
       </c>
     </row>
@@ -11539,30 +14021,30 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1883739</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Hart Lifts Ltd</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>-7.42</v>
+        <v>8.33</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>-7.42 — "E-billing Discount: 29/08/2025 - 28/11/2025"</t>
+          <t>Charged 14/11/2025 (15 days before period start); period 29/11/2025-28/02/2026; £8.33. "Repairs to lift controller unit"</t>
         </is>
       </c>
     </row>
@@ -11574,12 +14056,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -11589,15 +14071,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Hart Lifts Ltd</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>-1.03</v>
+        <v>5.48</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-1.03 — "Attended site to program numbers as requested"</t>
+          <t>Charged 21/11/2025 (8 days before period start); period 29/11/2025-28/02/2026; £5.48. "Renewed damaged lift door spring"</t>
         </is>
       </c>
     </row>
@@ -11609,30 +14091,30 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1933254</t>
+          <t>1968807</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Repairs</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>Integra Building Solutions Ltd</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>-7.42</v>
+        <v>2.57</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>-7.42 — "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+          <t>Charged 25/11/2025 (4 days before period start); period 29/11/2025-28/02/2026; £2.57. "Replace dry riser inlet lock"</t>
         </is>
       </c>
     </row>
@@ -11644,7 +14126,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11667,7 +14149,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>-7.72 — "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+          <t>Charged 01/03/2026 (1 days after period end); period 29/11/2025-28/02/2026; £-7.72. "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
         </is>
       </c>
     </row>
@@ -11679,7 +14161,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Credit / negative line</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11689,20 +14171,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Management Fee</t>
+          <t>Life System</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Newton Property Management Ltd</t>
+          <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>-7.72</v>
+        <v>0.31</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-7.72 — "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+          <t>Charged 31/01/2026 (29 days before period start); period 01/03/2026-28/05/2026; £0.31. "Door entry SIM card charge"</t>
         </is>
       </c>
     </row>
@@ -11714,7 +14196,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11722,15 +14204,22 @@
           <t>2013624</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HDN- NIG - 2025-2026</t>
-        </is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>5.53</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>'HDN- NIG - 2025-2026' billed in 2/3 prior quarters but is absent this quarter.</t>
+          <t>Charged 15/02/2026 (14 days before period start); period 01/03/2026-28/05/2026; £5.53. "Reset fire alarm system"</t>
         </is>
       </c>
     </row>
@@ -11742,7 +14231,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dropped vendor</t>
+          <t>Charge date outside invoice period</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11750,15 +14239,22 @@
           <t>2013624</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>VWS (UK) T/A Veolia Water Technologies</t>
-        </is>
+          <t>Hart Lifts Ltd</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>'VWS (UK) T/A Veolia Water Technologies' billed in 2/3 prior quarters but is absent this quarter.</t>
+          <t>Charged 30/01/2026 (30 days before period start); period 01/03/2026-28/05/2026; £4.60. "Repairs to lift (mis-use)"</t>
         </is>
       </c>
     </row>
@@ -11770,35 +14266,777 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Charged 05/02/2026 (24 days before period start); period 01/03/2026-28/05/2026; £2.71. "Lower car park door reset code"</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Charged 16/02/2026 (13 days before period start); period 01/03/2026-28/05/2026; £13.20. "Repair to upper car park shutter"</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Charged 29/05/2026 (1 days after period end); period 01/03/2026-28/05/2026; £-7.72. "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Cleaning</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>KC Janitorial Ltd</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Charged 21/05/2026 (8 days before period start); period 29/05/2026-28/08/2026; £5.15. "Rubbish removal - pump room"</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Charged 07/05/2026 (22 days before period start); period 29/05/2026-28/08/2026; £1.69. "Emergency lighting test"</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Life System</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Charged 07/05/2026 (22 days before period start); period 29/05/2026-28/08/2026; £3.38. "Emergency lighting test"</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Ritchie Mackenzie &amp; Co Ltd</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Charged 30/04/2026 (29 days before period start); period 29/05/2026-28/08/2026; £5.83. "Service checks of 1x booster set"</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>ASD Electrical Contractors Ltd</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Charged 07/05/2026 (22 days before period start); period 29/05/2026-28/08/2026; £13.82. "Emergency lighting repair"</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Argyle Locksmiths</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Charged 07/05/2026 (22 days before period start); period 29/05/2026-28/08/2026; £8.39. "fit lock on cctv cupboard door"</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Hart Lifts Ltd</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>6.68</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Charged 22/05/2026 (7 days before period start); period 29/05/2026-28/08/2026; £6.68. "Loler defect works"</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PTM Security Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Charged 30/04/2026 (29 days before period start); period 29/05/2026-28/08/2026; £0.43. "Sim card charge for the GSM door access system"</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Charge date outside invoice period</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Charged 29/08/2026 (1 days after period end); period 29/05/2026-28/08/2026; £-7.72. "E-billing Discount: 29/08/2026 - 28/11/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>1883739</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-7.42 — "E-billing Discount: 29/08/2025 - 28/11/2025"</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-1.03 — "Attended site to program numbers as requested"</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>1933254</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>-7.42</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-7.42 — "E-billing Discount: 29/11/2025 - 28/02/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1968807</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-7.72 — "E-billing Discount: 01/03/2026 - 28/05/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-7.72 — "E-billing Discount: 29/05/2026 - 28/08/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Credit / negative line</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Newton Property Management Ltd</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>-7.72</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-7.72 — "E-billing Discount: 29/08/2026 - 28/11/2026"</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>HDN- NIG - 2025-2026</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>'HDN- NIG - 2025-2026' billed in 2/3 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2013624</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>VWS (UK) T/A Veolia Water Technologies</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>'VWS (UK) T/A Veolia Water Technologies' billed in 2/3 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>HDN- NIG - 2025-2026</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>'HDN- NIG - 2025-2026' billed in 2/4 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Dropped vendor</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2060244</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Integra Building Solutions Ltd</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>'Integra Building Solutions Ltd' billed in 3/4 prior quarters but is absent this quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>Stale service period</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>1883739</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>Life System</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E108" t="inlineStr">
         <is>
           <t>PTM Security Solutions Ltd</t>
         </is>
       </c>
-      <c r="F86" s="3" t="n">
+      <c r="F108" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Service period 01/04/2025-30/04/2025 ends 29 days before the invoice quarter starts (29/05/2025); £0.29. "Sim card charge for the GSM door access system: 01"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G86"/>
+  <autoFilter ref="A1:G108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>